--- a/healthcare_surveys/049_skincare_fragrance_free_preference_survey--healthcare_surveys.xlsx
+++ b/healthcare_surveys/049_skincare_fragrance_free_preference_survey--healthcare_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C77"/>
+  <dimension ref="A1:C76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'normal'}</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Normal'}</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'dry'}</t>
+          <t>dry</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Dry'}</t>
+          <t>Dry</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'oily'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Oily'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'combination'}</t>
+          <t>combination</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Combination'}</t>
+          <t>Combination</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'sensitive'}</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Sensitive'}</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'aging'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Aging'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'acne'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Acne'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'dullness'}</t>
+          <t>dullness</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Dullness'}</t>
+          <t>Dullness</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'hyper-pigmentation'}</t>
+          <t>hyper-pigmentation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Hyper-Pigmentation'}</t>
+          <t>Hyper-Pigmentation</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'large_pores'}</t>
+          <t>large_pores</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Large pores'}</t>
+          <t>Large pores</t>
         </is>
       </c>
     </row>
@@ -1140,29 +1140,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'pore_size_variation'}</t>
+          <t>pore_size_variation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Pore size variation'}</t>
+          <t>Pore size variation</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>skin_concerns_choices</t>
+          <t>fragrance_allergy_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'pore_size_variation'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Pore size variation'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1174,29 +1174,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fragrance_allergy_choices</t>
+          <t>fragrance_preference_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>Strong</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'strong'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Strong'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1242,29 +1242,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'light'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Light'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fragrance_preference_choices</t>
+          <t>skincare_product_use_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'face'}</t>
+          <t>body</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Face'}</t>
+          <t>Body</t>
         </is>
       </c>
     </row>
@@ -1293,29 +1293,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'body'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Body'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>skincare_product_use_choices</t>
+          <t>skin_condition_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'both'}</t>
+          <t>acne</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Both'}</t>
+          <t>Acne</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'acne'}</t>
+          <t>aging</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Acne'}</t>
+          <t>Aging</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'aging'}</t>
+          <t>dullness</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Aging'}</t>
+          <t>Dullness</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'dullness'}</t>
+          <t>hyper-pigmentation</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Dullness'}</t>
+          <t>Hyper-Pigmentation</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'hyper-pigmentation'}</t>
+          <t>oily</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Hyper-Pigmentation'}</t>
+          <t>Oily</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'oily'}</t>
+          <t>sensitive</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Oily'}</t>
+          <t>Sensitive</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'sensitive'}</t>
+          <t>rosacea</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Sensitive'}</t>
+          <t>Rosacea</t>
         </is>
       </c>
     </row>
@@ -1429,29 +1429,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'rosacea'}</t>
+          <t>eczema</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Rosacea'}</t>
+          <t>Eczema</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>skin_condition_choices</t>
+          <t>preferred_skincare_product_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'eczema'}</t>
+          <t>moisturizer</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Eczema'}</t>
+          <t>Moisturizer</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'moisturizer'}</t>
+          <t>toner</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Moisturizer'}</t>
+          <t>Toner</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'toner'}</t>
+          <t>exfoliator</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Toner'}</t>
+          <t>Exfoliator</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'exfoliator'}</t>
+          <t>sunscreen</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Exfoliator'}</t>
+          <t>Sunscreen</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'sunscreen'}</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Sunscreen'}</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
@@ -1531,29 +1531,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'serum'}</t>
+          <t>face_mask</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Serum'}</t>
+          <t>Face Mask</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>preferred_skincare_product_choices</t>
+          <t>preferred_fragrance_product_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'face_mask'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Face Mask'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>moisturizer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>Moisturizer</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'moisturizer'}</t>
+          <t>toner</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Moisturizer'}</t>
+          <t>Toner</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'toner'}</t>
+          <t>exfoliator</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Toner'}</t>
+          <t>Exfoliator</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'exfoliator'}</t>
+          <t>sunscreen</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Exfoliator'}</t>
+          <t>Sunscreen</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'sunscreen'}</t>
+          <t>serum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Sunscreen'}</t>
+          <t>Serum</t>
         </is>
       </c>
     </row>
@@ -1650,29 +1650,29 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'serum'}</t>
+          <t>face_mask</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Serum'}</t>
+          <t>Face Mask</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>preferred_fragrance_product_choices</t>
+          <t>skincare_frequency_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'face_mask'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Face Mask'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>as-needed</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>As-needed</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'as-needed'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'As-needed'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1718,29 +1718,29 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>skincare_frequency_choices</t>
+          <t>fragrance_frequency_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>as-needed</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>As-needed</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'as-needed'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'As-needed'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1786,29 +1786,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fragrance_frequency_choices</t>
+          <t>skincare_pain_level_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'light'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Light'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1854,29 +1854,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'moderate'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>skincare_pain_level_choices</t>
+          <t>fragrance_pain_level_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'severe'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Severe'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'light'}</t>
+          <t>moderate</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Light'}</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1922,29 +1922,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'moderate'}</t>
+          <t>severe</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Moderate'}</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>fragrance_pain_level_choices</t>
+          <t>skincare_pain_location_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'severe'}</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Severe'}</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'face'}</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Face'}</t>
+          <t>Neck</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'neck'}</t>
+          <t>hands</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Neck'}</t>
+          <t>Hands</t>
         </is>
       </c>
     </row>
@@ -1990,29 +1990,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'hands'}</t>
+          <t>body</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Hands'}</t>
+          <t>Body</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>skincare_pain_location_choices</t>
+          <t>fragrance_pain_location_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'body'}</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Body'}</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'face'}</t>
+          <t>neck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Face'}</t>
+          <t>Neck</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'neck'}</t>
+          <t>hands</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Neck'}</t>
+          <t>Hands</t>
         </is>
       </c>
     </row>
@@ -2058,29 +2058,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'hands'}</t>
+          <t>body</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'Hands'}</t>
+          <t>Body</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>fragrance_pain_location_choices</t>
+          <t>skincare_pain_duration_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'body'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Body'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>less_than_24_hours</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>Less than 24 hours</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_24_hours'}</t>
+          <t>24_hours_to_1_week</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 24 hours'}</t>
+          <t>24 hours to 1 week</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'24_hours_to_1_week'}</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': '24 hours to 1 week'}</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -2143,29 +2143,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_weeks'}</t>
+          <t>more_than_2_weeks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': '1-2 weeks'}</t>
+          <t>More than 2 weeks</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>skincare_pain_duration_choices</t>
+          <t>fragrance_pain_duration_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_2_weeks'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'More than 2 weeks'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>less_than_24_hours</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>Less than 24 hours</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_24_hours'}</t>
+          <t>24_hours_to_1_week</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 24 hours'}</t>
+          <t>24 hours to 1 week</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'label':_'24_hours_to_1_week'}</t>
+          <t>1-2_weeks</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'label': '24 hours to 1 week'}</t>
+          <t>1-2 weeks</t>
         </is>
       </c>
     </row>
@@ -2228,29 +2228,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_weeks'}</t>
+          <t>more_than_2_weeks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'label': '1-2 weeks'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>fragrance_pain_duration_choices</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>{'label':_'more_than_2_weeks'}</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>{'label': 'More than 2 weeks'}</t>
+          <t>More than 2 weeks</t>
         </is>
       </c>
     </row>
